--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffFlowExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffFlowExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>核对周期</t>
   </si>
@@ -94,6 +94,12 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>执行状态</t>
+  </si>
+  <si>
+    <t>执行完成时间</t>
+  </si>
+  <si>
     <t>{.checkMonth}</t>
   </si>
   <si>
@@ -155,6 +161,12 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.execStatusName}</t>
+  </si>
+  <si>
+    <t>{.finishTime}</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30.625" customWidth="1"/>
@@ -1144,7 +1156,7 @@
     <col min="20" max="20" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:21">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1208,70 +1220,82 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffFlowExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffFlowExport.xlsx
@@ -49,7 +49,7 @@
     <t>ERP_SKU</t>
   </si>
   <si>
-    <t>上月期末库存</t>
+    <t>本月期初</t>
   </si>
   <si>
     <t>签收上架</t>
@@ -79,10 +79,10 @@
     <t>即时库存</t>
   </si>
   <si>
-    <t>扣减次月数据</t>
-  </si>
-  <si>
-    <t>实际期末库存</t>
+    <t>扣减次月数量</t>
+  </si>
+  <si>
+    <t>即时期末库存</t>
   </si>
   <si>
     <t>差异数量</t>
